--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -935,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z636"/>
+  <dimension ref="A1:Z702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -72517,6 +72517,7626 @@
       <c r="Y636" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Patient ID</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Identifier of the patient the batch is made for.</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Traceability (none)</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>unique per batch/patient; encodes sequence</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V637" t="inlineStr">
+        <is>
+          <t>Patient ID</t>
+        </is>
+      </c>
+      <c r="W637" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X637" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y637" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Filtered Patient ID</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Patient identifier as filtered by the source workbook; links a batch to its patient.</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Traceability (none)</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>unique per batch/patient; encodes sequence</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>Filtered Patient ID</t>
+        </is>
+      </c>
+      <c r="W638" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X638" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y638" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Re-MFG: Batch ID</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Batch identifier of a re-manufactured batch.</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Traceability (none)</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>unique per batch/patient; encodes sequence</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>Re-MFG: Batch ID</t>
+        </is>
+      </c>
+      <c r="W639" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X639" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y639" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Re-MFG: Original Batch ID</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Batch identifier of the original batch a re-manufactured batch replaces.</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Traceability (none)</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>unique per batch/patient; encodes sequence</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>Re-MFG: Original Batch ID</t>
+        </is>
+      </c>
+      <c r="W640" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X640" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y640" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Material Number</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Material number of the product made; names the product and its presentation.</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Process design (protocol)</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>protocol changes are real but trivially separate periods</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>Material Number</t>
+        </is>
+      </c>
+      <c r="W641" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X641" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y641" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>MBR Variant</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Version of the master batch record the batch was made under.</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>Process design (protocol)</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>protocol changes are real but trivially separate periods</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V642" t="inlineStr">
+        <is>
+          <t>MBR Variant</t>
+        </is>
+      </c>
+      <c r="W642" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X642" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y642" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Process version or variant the batch was made with.</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>Process design (protocol)</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>protocol changes are real but trivially separate periods</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V643" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="W643" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X643" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y643" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Study Name</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Clinical study or commercial programme the batch belongs to.</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>Site / line / scheduling</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>site/line/scheduling may differ by period</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>Study Name</t>
+        </is>
+      </c>
+      <c r="W644" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X644" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y644" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Region the patient and batch belong to.</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Site / line / scheduling</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>site/line/scheduling may differ by period</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="W645" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X645" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y645" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Site Merged</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Data source site of the batch row, added by the build when the two sites' batch records are merged.</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Site / line / scheduling</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>site/line/scheduling may differ by period</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>Site Merged</t>
+        </is>
+      </c>
+      <c r="W646" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y646" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Shift (1st/2nd)</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>D0</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>0</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Shift (first or second) that ran the batch, as the batch record states it.</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Thaw, selection and culture seeding</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>Execution (operator)</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>site/line/scheduling may differ by period</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>Shift (1st/2nd)</t>
+        </is>
+      </c>
+      <c r="W647" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X647" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y647" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Total number of data points</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Count of filled fields in the batch record: data completeness, not a process value.</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Cross-process context</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Site / line / scheduling</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>calculation version changed over time</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>Total number of data points</t>
+        </is>
+      </c>
+      <c r="W648" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X648" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y648" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z648" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Date of Apheresis Receipt</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Starting material and patient</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Apheresis</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Date the apheresis material was received at manufacturing.</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Apheresis and incoming material</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>Date of Apheresis Receipt</t>
+        </is>
+      </c>
+      <c r="W649" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X649" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y649" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Date of Screening</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Starting material and patient</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Apheresis</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Date the patient was screened for the study or treatment.</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Apheresis and incoming material</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Clinical / patient record</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>Date of Screening</t>
+        </is>
+      </c>
+      <c r="W650" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X650" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y650" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Date of Enrollment</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Starting material and patient</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Apheresis</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Date the patient was enrolled.</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Apheresis and incoming material</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Clinical / patient record</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>Date of Enrollment</t>
+        </is>
+      </c>
+      <c r="W651" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X651" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y651" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Week Start</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>D0</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>0</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>First day of the week the batch started manufacturing; a calendar label.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Thaw, selection and culture seeding</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>Week Start</t>
+        </is>
+      </c>
+      <c r="W652" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X652" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y652" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z652" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Date of QA Release</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>12</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Date QA released the batch.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr">
+        <is>
+          <t>Date of QA Release</t>
+        </is>
+      </c>
+      <c r="W653" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X653" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y653" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Date of QP Release</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>12</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Date the qualified person certified the batch.</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>Date of QP Release</t>
+        </is>
+      </c>
+      <c r="W654" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X654" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y654" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Date of Receipt at Clinical Site</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Cryopreservation and logistics</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Post-Release</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>13</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Date the product arrived at the clinical site.</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Shipment and infusion</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>Date of Receipt at Clinical Site</t>
+        </is>
+      </c>
+      <c r="W655" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X655" t="inlineStr">
+        <is>
+          <t>Exclude (post-release)</t>
+        </is>
+      </c>
+      <c r="Y655" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Time VSV-g Sample Submitted</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Transduction</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>3</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Time the VSV-g sample was submitted for testing.</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Transduction and expansion seeding</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Process timing</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>Calendar / scheduling</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>directly encodes calendar time</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>Datetime (derive intervals; don't use raw)</t>
+        </is>
+      </c>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>Time VSV-g Sample Submitted</t>
+        </is>
+      </c>
+      <c r="W656" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X656" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y656" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex A</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>3</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Volume taken from G-Rex A for the VSV-g sample.</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Transduction and expansion seeding</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>Process input (actual)</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>Execution (operator)</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Per vessel</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex A</t>
+        </is>
+      </c>
+      <c r="W657" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X657" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Y657" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex B</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>3</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Volume taken from G-Rex B for the VSV-g sample.</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Transduction and expansion seeding</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>Process input (actual)</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>Execution (operator)</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>Per vessel</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex B</t>
+        </is>
+      </c>
+      <c r="W658" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X658" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Y658" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex A_1</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Operations and traceability</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>3</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>A second column of the volume taken from G-Rex A for the VSV-g sample, as the source workbook carries it.</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Transduction and expansion seeding</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>Process input (actual)</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Execution (operator)</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Per vessel</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>Volume of VSV-g Sampling (mL) G-Rex A</t>
+        </is>
+      </c>
+      <c r="W659" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X659" t="inlineStr">
+        <is>
+          <t>Include (redundant - representative preferred)</t>
+        </is>
+      </c>
+      <c r="Y659" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Pre-Activation Clump Post Massage Mitigation Effect</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Cell health and composition</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>1</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Whether massaging removed the clumps seen before activation.</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Activation</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Viability; purity; dose; potency</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>In-process measurement</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>Biological response</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>Visual inspection (operator)</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>Pre-Activation Clump Post Massage Mitigation Effect</t>
+        </is>
+      </c>
+      <c r="W660" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X660" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Y660" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Post-Activation Clump Post Massage Mitigation Effect</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Cell health and composition</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>1</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Whether massaging removed the clumps seen after activation.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Activation</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Viability; purity; dose; potency</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>In-process measurement</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>Biological response</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Visual inspection (operator)</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>Post-Activation Clump Post Massage Mitigation Effect</t>
+        </is>
+      </c>
+      <c r="W661" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X661" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Y661" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Clumping Present on D1 or D3?</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Cell health and composition</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>3</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Whether clumps were seen on day 1 or day 3.</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Activation</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Viability; purity; dose; potency</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>In-process measurement</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>Biological response</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>Clumping Present on D1 or D3?</t>
+        </is>
+      </c>
+      <c r="W662" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X662" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="Y662" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z662" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>FP Flow (% CD19+ and NK cells)</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Cell health and composition</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>11</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Share of CD19+ and NK cells in the final product by flow cytometry: the non-T-cell impurity.</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Viability; purity; dose; potency</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>CQA / release result</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Flow cytometry</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>Purity / composition</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>FP Flow (% CD19+ and NK cells)</t>
+        </is>
+      </c>
+      <c r="W663" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X663" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y663" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>D10 F&amp;F KIT 5</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Formulation and dose</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>10</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Traceability code of the fifth fill and finish kit used on day 10.</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Harvest, wash and final processing</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Actionable (planning only)</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Dose; concentration; post-thaw viability</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>Material lot ID</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>lots are consumed sequentially -&gt; proxy for date</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>D10 F&amp;F KIT</t>
+        </is>
+      </c>
+      <c r="W664" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X664" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y664" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Bag 1 Appearance of Primary Container (MES)</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>11</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Appearance of the primary container of bag 1, as the MES records it.</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>CQA / release result</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Per replicate</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Visual inspection (operator)</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>Safety / appearance</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>Bag 1 Appearance of Primary Container (MES)</t>
+        </is>
+      </c>
+      <c r="W665" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X665" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y665" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Bag 2 Appearance of Primary Container (MES)</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>11</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Appearance of the primary container of bag 2, as the MES records it.</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>CQA / release result</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Per replicate</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>Visual inspection (operator)</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>Safety / appearance</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>Bag 2 Appearance of Primary Container (MES)</t>
+        </is>
+      </c>
+      <c r="W666" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X666" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y666" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>c.cPDL_Old Formula</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Growth and expansion</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>D3-D10</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>10</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Cumulative population doublings D3 to D10 by the source's earlier formula.</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>Expansion across D3-D10</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>Dose; viability; potency</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>In-process measurement</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>Biological response</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>calculation version changed over time</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>cPDL (D3 to D10)</t>
+        </is>
+      </c>
+      <c r="W667" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X667" t="inlineStr">
+        <is>
+          <t>Exclude (leakage)</t>
+        </is>
+      </c>
+      <c r="Y667" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z667" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Dose (CAR+ viable cells/kg) (Y|N)</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Formulation and dose</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>10</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Whether the batch record holds a weight-based dose.</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>Harvest, wash and final processing</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Process design (protocol)</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>protocol changes are real but trivially separate periods</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>Dose (CAR+ viable cells/kg) (Y|N)</t>
+        </is>
+      </c>
+      <c r="W668" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X668" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y668" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z668" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Dose: Number of CAR+ Viable T-Cells (cells) (Y|N)</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Formulation and dose</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>10</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Whether the batch record holds a flat dose.</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>Harvest, wash and final processing</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>Context across quality attributes</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>Context / design factor</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>Process design (protocol)</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Calculated (derived)</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>protocol changes are real but trivially separate periods</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V669" t="inlineStr">
+        <is>
+          <t>Dose: Number of CAR+ Viable T-Cells (cells) (Y|N)</t>
+        </is>
+      </c>
+      <c r="W669" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X669" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y669" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z669" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Physicians Decision</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>11</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>The treating physician's decision on using the product.</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U670" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V670" t="inlineStr">
+        <is>
+          <t>Physicians Decision</t>
+        </is>
+      </c>
+      <c r="W670" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X670" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y670" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>QCDD</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>11</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>QC disposition field as the source workbook names it (definition to be confirmed).</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U671" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V671" t="inlineStr">
+        <is>
+          <t>QCDD</t>
+        </is>
+      </c>
+      <c r="W671" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y671" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>NC Open</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>11</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Open non-conformances on the batch.</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U672" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V672" t="inlineStr">
+        <is>
+          <t>NC Open</t>
+        </is>
+      </c>
+      <c r="W672" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X672" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y672" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>NC OOS/Termination</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>11</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Non-conformance raised for an out-of-specification result or a termination.</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U673" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V673" t="inlineStr">
+        <is>
+          <t>NC OOS/Termination</t>
+        </is>
+      </c>
+      <c r="W673" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X673" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y673" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>CAPA OOS/Termination</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>11</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>CAPA raised for an out-of-specification result or a termination.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U674" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V674" t="inlineStr">
+        <is>
+          <t>CAPA OOS/Termination</t>
+        </is>
+      </c>
+      <c r="W674" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X674" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y674" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>QP release status</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>11</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Release status given by the qualified person.</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>QP release status</t>
+        </is>
+      </c>
+      <c r="W675" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X675" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y675" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>OOS Type Calc</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>11</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Kind of out-of-specification result, as the source workbook calculates it.</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>OOS Type Calc</t>
+        </is>
+      </c>
+      <c r="W676" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X676" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y676" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z676" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Termination Day</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>11</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Process day a terminated batch was stopped on.</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>Termination Day</t>
+        </is>
+      </c>
+      <c r="W677" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X677" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y677" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Termination Reason</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>11</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Why the batch was terminated.</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V678" t="inlineStr">
+        <is>
+          <t>Termination Reason</t>
+        </is>
+      </c>
+      <c r="W678" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X678" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y678" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>OOS/Termination Comment</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>11</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Free-text comment on an out-of-specification result or a termination.</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V679" t="inlineStr">
+        <is>
+          <t>OOS/Termination Comment</t>
+        </is>
+      </c>
+      <c r="W679" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X679" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y679" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Expert Decision: Controllable/ Uncontrollable</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>11</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Expert judgement whether the failure was controllable.</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>Expert Decision: Controllable/ Uncontrollable</t>
+        </is>
+      </c>
+      <c r="W680" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X680" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y680" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>11</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Free-text comments on the batch.</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>Nominal, high-cardinality</t>
+        </is>
+      </c>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="W681" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X681" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y681" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Remanufacture Reason</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>11</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Why the batch was re-manufactured.</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V682" t="inlineStr">
+        <is>
+          <t>Remanufacture Reason</t>
+        </is>
+      </c>
+      <c r="W682" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X682" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y682" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>OOS (Y|N) Calc.</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>11</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Whether the batch had an out-of-specification result, as the source workbook calculates it.</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V683" t="inlineStr">
+        <is>
+          <t>OOS (Y|N) Calc.</t>
+        </is>
+      </c>
+      <c r="W683" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X683" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y683" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z683" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Termination (Y|N)</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>11</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Whether the batch was terminated.</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V684" t="inlineStr">
+        <is>
+          <t>Termination (Y|N)</t>
+        </is>
+      </c>
+      <c r="W684" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X684" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y684" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Growth Termination (Y|N)</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>11</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Whether the batch was terminated for insufficient growth.</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V685" t="inlineStr">
+        <is>
+          <t>Growth Termination (Y|N)</t>
+        </is>
+      </c>
+      <c r="W685" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X685" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y685" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Non-Conformance Type Calc.</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>11</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Kind of non-conformance, as the source workbook calculates it.</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V686" t="inlineStr">
+        <is>
+          <t>Non-Conformance Type Calc.</t>
+        </is>
+      </c>
+      <c r="W686" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X686" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y686" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z686" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Batch terminated during manufacturing? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>11</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Whether the batch was terminated during manufacturing.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>Batch terminated during manufacturing? (Y/N)</t>
+        </is>
+      </c>
+      <c r="W687" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X687" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y687" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>EU/Canada Non Conformance Type</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>11</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Kind of non-conformance under the EU and Canadian definitions.</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>EU/Canada Non Conformance Type</t>
+        </is>
+      </c>
+      <c r="W688" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X688" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y688" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>EU/Canada OOS Type</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>11</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Kind of out-of-specification result under the EU and Canadian definitions.</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr">
+        <is>
+          <t>EU/Canada OOS Type</t>
+        </is>
+      </c>
+      <c r="W689" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X689" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y689" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Terminated Process</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>11</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>The process step or process of a terminated batch.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>Nominal</t>
+        </is>
+      </c>
+      <c r="V690" t="inlineStr">
+        <is>
+          <t>Terminated Process</t>
+        </is>
+      </c>
+      <c r="W690" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X690" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y690" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>c.Possible In-Spec (for Mfg Summary Tab)</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Final Product</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>11</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Whether the batch could have been in specification, as the source's summary tab calculates it.</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>Final-product testing or disposition</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>Overall disposition</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Disposition flag</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>symptom of the shift, not a cause</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>c.Possible In-Spec (for Mfg Summary Tab)</t>
+        </is>
+      </c>
+      <c r="W691" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X691" t="inlineStr">
+        <is>
+          <t>Exclude (outcome - analyse separately)</t>
+        </is>
+      </c>
+      <c r="Y691" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z691" t="inlineStr">
+        <is>
+          <t>source record</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Infused? (Y/N)</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Post-Release</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>13</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Whether the product was infused.</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>Shipment and infusion</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Logistics (post-release)</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>post-release; scheduling-driven</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>Infused? (Y/N)</t>
+        </is>
+      </c>
+      <c r="W692" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X692" t="inlineStr">
+        <is>
+          <t>Exclude (post-release)</t>
+        </is>
+      </c>
+      <c r="Y692" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Withdrawn (Y|N)</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Quality and disposition</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Post-Release</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>13</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Whether the patient or the product was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>Shipment and infusion</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>categorical</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>Attribute named in field; product disposition</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Disposition label</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Logistics (post-release)</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Batch record entry</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>post-release; scheduling-driven</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>Withdrawn (Y|N)</t>
+        </is>
+      </c>
+      <c r="W693" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X693" t="inlineStr">
+        <is>
+          <t>Exclude (post-release)</t>
+        </is>
+      </c>
+      <c r="Y693" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>LV CoA Delivered Dose per GRex</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>3</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Functional dose of vector delivered per G-Rex.</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>`LV Titer (unadjusted)` (else `LV Titer`) × `Volume`</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>LV CoA Delivered Dose per GRex</t>
+        </is>
+      </c>
+      <c r="W694" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X694" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y694" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z694" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>LV CoA Delivered Dose used adj titer</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>3</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>1 where the delivered dose fell back to the adjusted titer, else 0.</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>1 if `LV Titer (unadjusted)` is missing, else 0</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>Binary</t>
+        </is>
+      </c>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>LV CoA Delivered Dose used adj titer</t>
+        </is>
+      </c>
+      <c r="W695" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X695" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y695" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z695" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>LV CoA Titer Adjustment Factor</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>3</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>How hard the release titer was corrected.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>`LV Titer` / `LV Titer (unadjusted)`</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>LV CoA Titer Adjustment Factor</t>
+        </is>
+      </c>
+      <c r="W696" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X696" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y696" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z696" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>LV CoA Specific Infectivity</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>3</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Infectious titer per physical particle.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>`LV Titer` / `Physical Titer p24 ELISA`</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>LV CoA Specific Infectivity</t>
+        </is>
+      </c>
+      <c r="W697" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X697" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y697" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z697" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>LV CoA E1b Fraction of Total DNA</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>3</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>The last residual-DNA species as a share of all residual DNA.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>`E1b cDNA` / Σ(`pDNA`, `cDNA`, `E1a cDNA`, `E1b cDNA`)</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>LV CoA E1b Fraction of Total DNA</t>
+        </is>
+      </c>
+      <c r="W698" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X698" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y698" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z698" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>LV CoA pH Abs Deviation</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>3</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Distance of the vector pH from the spec midpoint.</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>|`pH` − lv_coa.ph_nominal|</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>LV CoA pH Abs Deviation</t>
+        </is>
+      </c>
+      <c r="W699" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X699" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y699" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z699" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>LV CoA Osmolality Abs Deviation</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>3</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Distance of the vector osmolality from the spec midpoint.</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>|`Osmolality` − lv_coa.osmo_nominal|</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>LV CoA Osmolality Abs Deviation</t>
+        </is>
+      </c>
+      <c r="W700" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="X700" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y700" t="inlineStr">
+        <is>
+          <t>Engineered</t>
+        </is>
+      </c>
+      <c r="Z700" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>LV CoA CAR% Donor DIFF Rel</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>3</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Disagreement of the two reference donors' CAR%, relative to their mean.</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>(max − min) / mean of donor 1 and donor 2</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>LV CoA CAR%</t>
+        </is>
+      </c>
+      <c r="W701" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X701" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y701" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z701" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>LV CoA IFNg Donor DIFF Rel</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Vector quality</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Vector CoA</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>3</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Disagreement of the two reference donors' IFNg, relative to their mean.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>Vector qualification before use</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Not actionable</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>CAR%; VCN; potency; safety</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Existing derived metric</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>(max − min) / mean of donor 1 and donor 2</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Material attribute</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Raw material / vector</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Material lot</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Supplier / vector CoA</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>constant within a lot -&gt; lot fingerprint</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>LV CoA IFNg</t>
+        </is>
+      </c>
+      <c r="W702" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="X702" t="inlineStr">
+        <is>
+          <t>Review (stratify or include deliberately)</t>
+        </is>
+      </c>
+      <c r="Y702" t="inlineStr">
+        <is>
+          <t>Normalization</t>
+        </is>
+      </c>
+      <c r="Z702" t="inlineStr">
+        <is>
+          <t>pipeline (vector certificate loader)</t>
         </is>
       </c>
     </row>
